--- a/04_Figures/F04_association/modules/trajectory/spearman/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/trajectory/spearman/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -71,12 +71,6 @@
     <t xml:space="preserve">ME_red@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T1</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_turquoise@T1</t>
   </si>
   <si>
@@ -110,12 +104,6 @@
     <t xml:space="preserve">ME_red@T2</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_turquoise@T2</t>
   </si>
   <si>
@@ -147,12 +135,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T3</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise@T3</t>
@@ -566,16 +548,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0989010989010989</v>
+        <v>-0.032967032967033</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.344291425054203</v>
+        <v>-0.114263261126781</v>
       </c>
       <c r="F2" t="n">
-        <v>0.736585369925317</v>
+        <v>0.910918653071845</v>
       </c>
       <c r="G2" t="n">
-        <v>0.971396838655591</v>
+        <v>0.934618994603643</v>
       </c>
     </row>
     <row r="3">
@@ -589,16 +571,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00659340659340659</v>
+        <v>0.283516483516484</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0228407269124562</v>
+        <v>1.0241536325576</v>
       </c>
       <c r="F3" t="n">
-        <v>0.98215273545779</v>
+        <v>0.325965947441773</v>
       </c>
       <c r="G3" t="n">
-        <v>0.98215273545779</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="4">
@@ -612,16 +594,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0989010989010989</v>
+        <v>0.134065934065934</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.344291425054203</v>
+        <v>0.468648785948378</v>
       </c>
       <c r="F4" t="n">
-        <v>0.736585369925317</v>
+        <v>0.647719527985113</v>
       </c>
       <c r="G4" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="5">
@@ -635,16 +617,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2</v>
+        <v>0.0637362637362637</v>
       </c>
       <c r="E5" t="n">
-        <v>0.707106781186548</v>
+        <v>0.221238721732763</v>
       </c>
       <c r="F5" t="n">
-        <v>0.49300373504</v>
+        <v>0.828626422928612</v>
       </c>
       <c r="G5" t="n">
-        <v>0.971396838655591</v>
+        <v>0.934618994603643</v>
       </c>
     </row>
     <row r="6">
@@ -658,16 +640,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.384615384615385</v>
+        <v>-0.362637362637363</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.44337567297406</v>
+        <v>-1.34796843802067</v>
       </c>
       <c r="F6" t="n">
-        <v>0.174508750775096</v>
+        <v>0.202564543817242</v>
       </c>
       <c r="G6" t="n">
-        <v>0.850172353457534</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="7">
@@ -681,16 +663,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.56043956043956</v>
+        <v>-0.0989010989010989</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3441566548623</v>
+        <v>-0.344291425054203</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0371044770040744</v>
+        <v>0.736585369925317</v>
       </c>
       <c r="G7" t="n">
-        <v>0.482358201052967</v>
+        <v>0.900271007686499</v>
       </c>
     </row>
     <row r="8">
@@ -704,16 +686,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.164835164835165</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E8" t="n">
-        <v>0.578924798693409</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.573346405013138</v>
+        <v>0.626117476225324</v>
       </c>
       <c r="G8" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="9">
@@ -727,16 +709,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0285714285714286</v>
+        <v>0.173626373626374</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0990147542976674</v>
+        <v>0.61073549793191</v>
       </c>
       <c r="F9" t="n">
-        <v>0.922761376569875</v>
+        <v>0.552766941142241</v>
       </c>
       <c r="G9" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="10">
@@ -750,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0285714285714286</v>
+        <v>0.217582417582418</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0990147542976674</v>
+        <v>0.772228696551556</v>
       </c>
       <c r="F10" t="n">
-        <v>0.922761376569875</v>
+        <v>0.454919373170033</v>
       </c>
       <c r="G10" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="11">
@@ -773,16 +755,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.358241758241758</v>
+        <v>-0.125274725274725</v>
       </c>
       <c r="E11" t="n">
-        <v>1.32920682989838</v>
+        <v>-0.437410256409312</v>
       </c>
       <c r="F11" t="n">
-        <v>0.208498124790767</v>
+        <v>0.669582396544844</v>
       </c>
       <c r="G11" t="n">
-        <v>0.850172353457534</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="12">
@@ -796,16 +778,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.410989010989011</v>
+        <v>-0.208791208791209</v>
       </c>
       <c r="E12" t="n">
-        <v>1.56169895075115</v>
+        <v>-0.739573996953447</v>
       </c>
       <c r="F12" t="n">
-        <v>0.144332668124605</v>
+        <v>0.473778837309814</v>
       </c>
       <c r="G12" t="n">
-        <v>0.850172353457534</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="13">
@@ -819,16 +801,16 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.12967032967033</v>
+        <v>-0.0285714285714286</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.453015938607022</v>
+        <v>-0.0990147542976674</v>
       </c>
       <c r="F13" t="n">
-        <v>0.658619276321178</v>
+        <v>0.922761376569875</v>
       </c>
       <c r="G13" t="n">
-        <v>0.971396838655591</v>
+        <v>0.934618994603643</v>
       </c>
     </row>
     <row r="14">
@@ -842,16 +824,16 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>0.221978021978022</v>
+        <v>0.243956043956044</v>
       </c>
       <c r="E14" t="n">
-        <v>0.788629411844184</v>
+        <v>0.871417274558076</v>
       </c>
       <c r="F14" t="n">
-        <v>0.445629657953609</v>
+        <v>0.400624803916119</v>
       </c>
       <c r="G14" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="15">
@@ -865,16 +847,16 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>0.191208791208791</v>
+        <v>0.164835164835165</v>
       </c>
       <c r="E15" t="n">
-        <v>0.674817478932826</v>
+        <v>0.578924798693409</v>
       </c>
       <c r="F15" t="n">
-        <v>0.512583970470779</v>
+        <v>0.573346405013138</v>
       </c>
       <c r="G15" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="16">
@@ -888,16 +870,16 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0241758241758242</v>
+        <v>-0.103296703296703</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0837719962821407</v>
+        <v>-0.359754753325688</v>
       </c>
       <c r="F16" t="n">
-        <v>0.934618994603643</v>
+        <v>0.725282211088945</v>
       </c>
       <c r="G16" t="n">
-        <v>0.971396838655591</v>
+        <v>0.900271007686499</v>
       </c>
     </row>
     <row r="17">
@@ -911,16 +893,16 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.204395604395604</v>
+        <v>0.0285714285714286</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.723317557443421</v>
+        <v>0.0990147542976674</v>
       </c>
       <c r="F17" t="n">
-        <v>0.483346223042223</v>
+        <v>0.922761376569875</v>
       </c>
       <c r="G17" t="n">
-        <v>0.971396838655591</v>
+        <v>0.934618994603643</v>
       </c>
     </row>
     <row r="18">
@@ -934,16 +916,16 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0.336263736263736</v>
+        <v>0.151648351648352</v>
       </c>
       <c r="E18" t="n">
-        <v>1.23687779440215</v>
+        <v>0.531472035224587</v>
       </c>
       <c r="F18" t="n">
-        <v>0.239792202257253</v>
+        <v>0.604790598452137</v>
       </c>
       <c r="G18" t="n">
-        <v>0.850172353457534</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="19">
@@ -957,16 +939,16 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0549450549450549</v>
+        <v>0.147252747252747</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.190623212915756</v>
+        <v>0.515720400699903</v>
       </c>
       <c r="F19" t="n">
-        <v>0.852007703632368</v>
+        <v>0.615418762484725</v>
       </c>
       <c r="G19" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="20">
@@ -980,16 +962,16 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0241758241758242</v>
+        <v>0.204395604395604</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0837719962821407</v>
+        <v>0.723317557443421</v>
       </c>
       <c r="F20" t="n">
-        <v>0.934618994603643</v>
+        <v>0.483346223042223</v>
       </c>
       <c r="G20" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="21">
@@ -1003,16 +985,16 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.252747252747253</v>
+        <v>0.134065934065934</v>
       </c>
       <c r="E21" t="n">
-        <v>0.904922896669329</v>
+        <v>0.468648785948378</v>
       </c>
       <c r="F21" t="n">
-        <v>0.383314964478511</v>
+        <v>0.647719527985113</v>
       </c>
       <c r="G21" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="22">
@@ -1026,16 +1008,16 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0945054945054945</v>
+        <v>-0.142857142857143</v>
       </c>
       <c r="E22" t="n">
-        <v>0.328848450013655</v>
+        <v>-0.5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.747938261141548</v>
+        <v>0.626117476225324</v>
       </c>
       <c r="G22" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="23">
@@ -1049,16 +1031,16 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.164835164835165</v>
+        <v>-0.287912087912088</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.578924798693409</v>
+        <v>-1.04145523072203</v>
       </c>
       <c r="F23" t="n">
-        <v>0.573346405013138</v>
+        <v>0.3181928710258</v>
       </c>
       <c r="G23" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="24">
@@ -1072,16 +1054,16 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0945054945054945</v>
+        <v>-0.252747252747253</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.328848450013655</v>
+        <v>-0.904922896669329</v>
       </c>
       <c r="F24" t="n">
-        <v>0.747938261141548</v>
+        <v>0.383314964478511</v>
       </c>
       <c r="G24" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="25">
@@ -1095,16 +1077,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.274725274725275</v>
+        <v>-0.0549450549450549</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.98975947808112</v>
+        <v>-0.190623212915756</v>
       </c>
       <c r="F25" t="n">
-        <v>0.341829743719481</v>
+        <v>0.852007703632368</v>
       </c>
       <c r="G25" t="n">
-        <v>0.971396838655591</v>
+        <v>0.934618994603643</v>
       </c>
     </row>
     <row r="26">
@@ -1118,16 +1100,16 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.147252747252747</v>
+        <v>-0.446153846153846</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.515720400699903</v>
+        <v>-1.7269248691087</v>
       </c>
       <c r="F26" t="n">
-        <v>0.615418762484725</v>
+        <v>0.109807127801225</v>
       </c>
       <c r="G26" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="27">
@@ -1141,16 +1123,16 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0681318681318681</v>
+        <v>0.454945054945055</v>
       </c>
       <c r="E27" t="n">
-        <v>0.236565415689409</v>
+        <v>1.76972641547089</v>
       </c>
       <c r="F27" t="n">
-        <v>0.816983879781792</v>
+        <v>0.102153526691829</v>
       </c>
       <c r="G27" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="28">
@@ -1164,16 +1146,16 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0197802197802198</v>
+        <v>-0.169230769230769</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0685340998265018</v>
+        <v>-0.594811877479463</v>
       </c>
       <c r="F28" t="n">
-        <v>0.946489227408011</v>
+        <v>0.563017273996211</v>
       </c>
       <c r="G28" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="29">
@@ -1187,16 +1169,16 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.516483516483516</v>
+        <v>-0.0241758241758242</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.08940485502962</v>
+        <v>-0.0837719962821407</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0586371634412785</v>
+        <v>0.934618994603643</v>
       </c>
       <c r="G29" t="n">
-        <v>0.571712343552466</v>
+        <v>0.934618994603643</v>
       </c>
     </row>
     <row r="30">
@@ -1210,16 +1192,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.621978021978022</v>
+        <v>0.617582417582418</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.75159590331243</v>
+        <v>2.72009086297656</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01755031529054</v>
+        <v>0.0186046742807084</v>
       </c>
       <c r="G30" t="n">
-        <v>0.482358201052967</v>
+        <v>0.306977125631689</v>
       </c>
     </row>
     <row r="31">
@@ -1233,16 +1215,16 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0373626373626374</v>
+        <v>0.235164835164835</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.12951840569399</v>
+        <v>0.838140102702703</v>
       </c>
       <c r="F31" t="n">
-        <v>0.899093096973967</v>
+        <v>0.418333896198592</v>
       </c>
       <c r="G31" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="32">
@@ -1256,16 +1238,16 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.164835164835165</v>
+        <v>-0.186813186813187</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.578924798693409</v>
+        <v>-0.658736619548309</v>
       </c>
       <c r="F32" t="n">
-        <v>0.573346405013138</v>
+        <v>0.522504012379159</v>
       </c>
       <c r="G32" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="33">
@@ -1279,16 +1261,16 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0813186813186813</v>
+        <v>0.305494505494505</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.282632210255267</v>
+        <v>1.11139556517412</v>
       </c>
       <c r="F33" t="n">
-        <v>0.782274751244096</v>
+        <v>0.288169885875457</v>
       </c>
       <c r="G33" t="n">
-        <v>0.971396838655591</v>
+        <v>0.883848763439195</v>
       </c>
     </row>
     <row r="34">
@@ -1302,154 +1284,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.349450549450549</v>
+        <v>-0.621978021978022</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2919856983087</v>
+        <v>-2.75159590331243</v>
       </c>
       <c r="F34" t="n">
-        <v>0.220689997746447</v>
+        <v>0.01755031529054</v>
       </c>
       <c r="G34" t="n">
-        <v>0.850172353457534</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.578021978021978</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2.45376820670907</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.030383014145237</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.482358201052967</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.428571428571429</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1.6431676725155</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.126273888159313</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.850172353457534</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0285714285714286</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.0990147542976674</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.922761376569875</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.971396838655591</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.362637362637363</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1.34796843802067</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.202564543817242</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.850172353457534</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.305494505494505</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.11139556517412</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.288169885875457</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.936552129095236</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.12967032967033</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.453015938607022</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.658619276321178</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.971396838655591</v>
+        <v>0.306977125631689</v>
       </c>
     </row>
   </sheetData>
@@ -1488,7 +1332,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1497,21 +1341,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.12967032967033</v>
+        <v>0.00659340659340659</v>
       </c>
       <c r="E2" t="n">
-        <v>0.453015938607022</v>
+        <v>0.0228407269124562</v>
       </c>
       <c r="F2" t="n">
-        <v>0.658619276321178</v>
+        <v>0.98215273545779</v>
       </c>
       <c r="G2" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -1520,21 +1364,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.116483516483516</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.406276413480895</v>
+        <v>0.344291425054203</v>
       </c>
       <c r="F3" t="n">
-        <v>0.691691250233157</v>
+        <v>0.736585369925317</v>
       </c>
       <c r="G3" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1543,21 +1387,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0901098901098901</v>
+        <v>-0.0813186813186813</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.313424881933839</v>
+        <v>-0.282632210255267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.759338837815954</v>
+        <v>0.782274751244096</v>
       </c>
       <c r="G4" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -1566,21 +1410,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.032967032967033</v>
+        <v>-0.0593406593406593</v>
       </c>
       <c r="E5" t="n">
-        <v>0.114263261126781</v>
+        <v>-0.20592495680455</v>
       </c>
       <c r="F5" t="n">
-        <v>0.910918653071845</v>
+        <v>0.840301762690683</v>
       </c>
       <c r="G5" t="n">
-        <v>0.958369789371986</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -1589,21 +1433,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.125274725274725</v>
+        <v>-0.103296703296703</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.437410256409312</v>
+        <v>-0.359754753325688</v>
       </c>
       <c r="F6" t="n">
-        <v>0.669582396544844</v>
+        <v>0.725282211088945</v>
       </c>
       <c r="G6" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -1612,21 +1456,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.459340659340659</v>
+        <v>0.12967032967033</v>
       </c>
       <c r="E7" t="n">
-        <v>1.79137007866669</v>
+        <v>0.453015938607022</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0984683761682903</v>
+        <v>0.658619276321178</v>
       </c>
       <c r="G7" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -1635,21 +1479,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.217582417582418</v>
+        <v>0.257142857142857</v>
       </c>
       <c r="E8" t="n">
-        <v>0.772228696551556</v>
+        <v>0.92176480169854</v>
       </c>
       <c r="F8" t="n">
-        <v>0.454919373170033</v>
+        <v>0.37481190387997</v>
       </c>
       <c r="G8" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -1658,21 +1502,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.213186813186813</v>
+        <v>0.12967032967033</v>
       </c>
       <c r="E9" t="n">
-        <v>0.755877303492696</v>
+        <v>0.453015938607022</v>
       </c>
       <c r="F9" t="n">
-        <v>0.464302820039744</v>
+        <v>0.658619276321178</v>
       </c>
       <c r="G9" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -1681,21 +1525,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0945054945054945</v>
+        <v>0.0241758241758242</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.328848450013655</v>
+        <v>0.0837719962821407</v>
       </c>
       <c r="F10" t="n">
-        <v>0.747938261141548</v>
+        <v>0.934618994603643</v>
       </c>
       <c r="G10" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -1704,21 +1548,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.305494505494505</v>
+        <v>-0.032967032967033</v>
       </c>
       <c r="E11" t="n">
-        <v>1.11139556517412</v>
+        <v>-0.114263261126781</v>
       </c>
       <c r="F11" t="n">
-        <v>0.288169885875457</v>
+        <v>0.910918653071845</v>
       </c>
       <c r="G11" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -1727,21 +1571,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0945054945054945</v>
+        <v>-0.217582417582418</v>
       </c>
       <c r="E12" t="n">
-        <v>0.328848450013655</v>
+        <v>-0.772228696551556</v>
       </c>
       <c r="F12" t="n">
-        <v>0.747938261141548</v>
+        <v>0.454919373170033</v>
       </c>
       <c r="G12" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -1750,21 +1594,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0241758241758242</v>
+        <v>0.147252747252747</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0837719962821407</v>
+        <v>0.515720400699903</v>
       </c>
       <c r="F13" t="n">
-        <v>0.934618994603643</v>
+        <v>0.615418762484725</v>
       </c>
       <c r="G13" t="n">
-        <v>0.958369789371986</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -1773,21 +1617,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0945054945054945</v>
+        <v>0.0021978021978022</v>
       </c>
       <c r="E14" t="n">
-        <v>0.328848450013655</v>
+        <v>0.00761342853088536</v>
       </c>
       <c r="F14" t="n">
-        <v>0.747938261141548</v>
+        <v>0.9940505286659</v>
       </c>
       <c r="G14" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -1796,21 +1640,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>0.367032967032967</v>
+        <v>0.243956043956044</v>
       </c>
       <c r="E15" t="n">
-        <v>1.36683363683457</v>
+        <v>0.871417274558076</v>
       </c>
       <c r="F15" t="n">
-        <v>0.196738871707488</v>
+        <v>0.400624803916119</v>
       </c>
       <c r="G15" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -1819,21 +1663,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>0.107692307692308</v>
+        <v>-0.120879120879121</v>
       </c>
       <c r="E16" t="n">
-        <v>0.375239387193228</v>
+        <v>-0.421830743866054</v>
       </c>
       <c r="F16" t="n">
-        <v>0.714030808726249</v>
+        <v>0.680607020062893</v>
       </c>
       <c r="G16" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -1842,21 +1686,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.182417582417582</v>
+        <v>0.182417582417582</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.642696755708738</v>
+        <v>0.642696755708738</v>
       </c>
       <c r="F17" t="n">
         <v>0.532508818518694</v>
       </c>
       <c r="G17" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -1865,21 +1709,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0285714285714286</v>
+        <v>0.314285714285714</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0990147542976674</v>
+        <v>1.14682927731391</v>
       </c>
       <c r="F18" t="n">
-        <v>0.922761376569875</v>
+        <v>0.273804902962868</v>
       </c>
       <c r="G18" t="n">
-        <v>0.958369789371986</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -1888,21 +1732,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.112087912087912</v>
+        <v>0.371428571428571</v>
       </c>
       <c r="E19" t="n">
-        <v>0.390746285420994</v>
+        <v>1.38580465631147</v>
       </c>
       <c r="F19" t="n">
-        <v>0.70283316319677</v>
+        <v>0.191020812043616</v>
       </c>
       <c r="G19" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -1911,21 +1755,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.230769230769231</v>
+        <v>0.362637362637363</v>
       </c>
       <c r="E20" t="n">
-        <v>0.821583836257749</v>
+        <v>1.34796843802067</v>
       </c>
       <c r="F20" t="n">
-        <v>0.42733586167745</v>
+        <v>0.202564543817242</v>
       </c>
       <c r="G20" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -1934,21 +1778,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.468131868131868</v>
+        <v>-0.0241758241758242</v>
       </c>
       <c r="E21" t="n">
-        <v>1.83516159583906</v>
+        <v>-0.0837719962821407</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0913763650683312</v>
+        <v>0.934618994603643</v>
       </c>
       <c r="G21" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -1957,21 +1801,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.358241758241758</v>
+        <v>-0.243956043956044</v>
       </c>
       <c r="E22" t="n">
-        <v>1.32920682989838</v>
+        <v>-0.871417274558076</v>
       </c>
       <c r="F22" t="n">
-        <v>0.208498124790767</v>
+        <v>0.400624803916119</v>
       </c>
       <c r="G22" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -1980,21 +1824,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.235164835164835</v>
+        <v>-0.248351648351648</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.838140102702703</v>
+        <v>-0.888140849482722</v>
       </c>
       <c r="F23" t="n">
-        <v>0.418333896198592</v>
+        <v>0.391919538938457</v>
       </c>
       <c r="G23" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -2003,21 +1847,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0989010989010989</v>
+        <v>0.0901098901098901</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.344291425054203</v>
+        <v>0.313424881933839</v>
       </c>
       <c r="F24" t="n">
-        <v>0.736585369925317</v>
+        <v>0.759338837815954</v>
       </c>
       <c r="G24" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -2026,21 +1870,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.340659340659341</v>
+        <v>-0.296703296703297</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.25515331177732</v>
+        <v>-1.07627535699179</v>
       </c>
       <c r="F25" t="n">
-        <v>0.233316051036824</v>
+        <v>0.302966723838702</v>
       </c>
       <c r="G25" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -2049,21 +1893,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.230769230769231</v>
+        <v>-0.0241758241758242</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.821583836257749</v>
+        <v>-0.0837719962821407</v>
       </c>
       <c r="F26" t="n">
-        <v>0.42733586167745</v>
+        <v>0.934618994603643</v>
       </c>
       <c r="G26" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -2072,21 +1916,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.032967032967033</v>
+        <v>0.178021978021978</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.114263261126781</v>
+        <v>0.626696755002979</v>
       </c>
       <c r="F27" t="n">
-        <v>0.910918653071845</v>
+        <v>0.542596952606215</v>
       </c>
       <c r="G27" t="n">
-        <v>0.958369789371986</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -2095,21 +1939,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.169230769230769</v>
+        <v>0.173626373626374</v>
       </c>
       <c r="E28" t="n">
-        <v>0.594811877479463</v>
+        <v>0.61073549793191</v>
       </c>
       <c r="F28" t="n">
-        <v>0.563017273996211</v>
+        <v>0.552766941142241</v>
       </c>
       <c r="G28" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -2118,21 +1962,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.138461538461538</v>
+        <v>0.107692307692308</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.484309802250568</v>
+        <v>0.375239387193228</v>
       </c>
       <c r="F29" t="n">
-        <v>0.636884991265018</v>
+        <v>0.714030808726249</v>
       </c>
       <c r="G29" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -2141,21 +1985,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.340659340659341</v>
+        <v>0.516483516483516</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.25515331177732</v>
+        <v>2.08940485502962</v>
       </c>
       <c r="F30" t="n">
-        <v>0.233316051036824</v>
+        <v>0.0586371634412785</v>
       </c>
       <c r="G30" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -2164,21 +2008,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.305494505494505</v>
+        <v>0.432967032967033</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.11139556517412</v>
+        <v>1.66388458531666</v>
       </c>
       <c r="F31" t="n">
-        <v>0.288169885875457</v>
+        <v>0.12201000596848</v>
       </c>
       <c r="G31" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -2187,21 +2031,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>0.186813186813187</v>
+        <v>-0.243956043956044</v>
       </c>
       <c r="E32" t="n">
-        <v>0.658736619548309</v>
+        <v>-0.871417274558076</v>
       </c>
       <c r="F32" t="n">
-        <v>0.522504012379159</v>
+        <v>0.400624803916119</v>
       </c>
       <c r="G32" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -2210,21 +2054,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>0.265934065934066</v>
+        <v>0.0153846153846154</v>
       </c>
       <c r="E33" t="n">
-        <v>0.955633835704927</v>
+        <v>0.0533001790889026</v>
       </c>
       <c r="F33" t="n">
-        <v>0.358113400364786</v>
+        <v>0.958369789371986</v>
       </c>
       <c r="G33" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -2233,154 +2077,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.516483516483516</v>
+        <v>-0.327472527472527</v>
       </c>
       <c r="E34" t="n">
-        <v>2.08940485502962</v>
+        <v>-1.20059825800301</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0586371634412785</v>
+        <v>0.25307100077194</v>
       </c>
       <c r="G34" t="n">
-        <v>0.871006313965359</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.463736263736264</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.81318054513692</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0948763315088996</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.871006313965359</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.142857142857143</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.626117476225324</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.871006313965359</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.134065934065934</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.468648785948378</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.647719527985113</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.871006313965359</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.138461538461538</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.484309802250568</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.636884991265018</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.871006313965359</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.0153846153846154</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.0533001790889026</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.958369789371986</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.958369789371986</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.208791208791209</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.739573996953447</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.473778837309814</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.871006313965359</v>
+        <v>0.9940505286659</v>
       </c>
     </row>
   </sheetData>
@@ -2419,7 +2125,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2437,12 +2143,12 @@
         <v>0.828626422928612</v>
       </c>
       <c r="G2" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2451,21 +2157,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0373626373626374</v>
+        <v>0.169230769230769</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.12951840569399</v>
+        <v>0.594811877479463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.899093096973967</v>
+        <v>0.563017273996211</v>
       </c>
       <c r="G3" t="n">
-        <v>0.98215273545779</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2474,21 +2180,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.169230769230769</v>
+        <v>-0.0725274725274725</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.594811877479463</v>
+        <v>-0.251905950462024</v>
       </c>
       <c r="F4" t="n">
-        <v>0.563017273996211</v>
+        <v>0.805376313541092</v>
       </c>
       <c r="G4" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2497,21 +2203,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0945054945054945</v>
+        <v>-0.0813186813186813</v>
       </c>
       <c r="E5" t="n">
-        <v>0.328848450013655</v>
+        <v>-0.282632210255267</v>
       </c>
       <c r="F5" t="n">
-        <v>0.747938261141548</v>
+        <v>0.782274751244096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2520,21 +2226,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.265934065934066</v>
+        <v>-0.230769230769231</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.955633835704927</v>
+        <v>-0.821583836257749</v>
       </c>
       <c r="F6" t="n">
-        <v>0.358113400364786</v>
+        <v>0.42733586167745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2543,21 +2249,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.547252747252747</v>
+        <v>0.0637362637362637</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2650095129065</v>
+        <v>0.221238721732763</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0428220493781973</v>
+        <v>0.828626422928612</v>
       </c>
       <c r="G7" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2566,21 +2272,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.226373626373626</v>
+        <v>0.274725274725275</v>
       </c>
       <c r="E8" t="n">
-        <v>0.80508070183143</v>
+        <v>0.98975947808112</v>
       </c>
       <c r="F8" t="n">
-        <v>0.436434794556053</v>
+        <v>0.341829743719481</v>
       </c>
       <c r="G8" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2589,21 +2295,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.186813186813187</v>
+        <v>0.156043956043956</v>
       </c>
       <c r="E9" t="n">
-        <v>0.658736619548309</v>
+        <v>0.547255944180659</v>
       </c>
       <c r="F9" t="n">
-        <v>0.522504012379159</v>
+        <v>0.594234700580851</v>
       </c>
       <c r="G9" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2612,21 +2318,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.116483516483516</v>
+        <v>0.0725274725274725</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.406276413480895</v>
+        <v>0.251905950462024</v>
       </c>
       <c r="F10" t="n">
-        <v>0.691691250233157</v>
+        <v>0.805376313541092</v>
       </c>
       <c r="G10" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2635,21 +2341,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.345054945054945</v>
+        <v>-0.0549450549450549</v>
       </c>
       <c r="E11" t="n">
-        <v>1.27352194297108</v>
+        <v>-0.190623212915756</v>
       </c>
       <c r="F11" t="n">
-        <v>0.226948680041701</v>
+        <v>0.852007703632368</v>
       </c>
       <c r="G11" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2658,21 +2364,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.191208791208791</v>
+        <v>-0.305494505494505</v>
       </c>
       <c r="E12" t="n">
-        <v>0.674817478932826</v>
+        <v>-1.11139556517412</v>
       </c>
       <c r="F12" t="n">
-        <v>0.512583970470779</v>
+        <v>0.288169885875457</v>
       </c>
       <c r="G12" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -2681,21 +2387,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.032967032967033</v>
+        <v>0.0857142857142857</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.114263261126781</v>
+        <v>0.298019780339635</v>
       </c>
       <c r="F13" t="n">
-        <v>0.910918653071845</v>
+        <v>0.770785031118676</v>
       </c>
       <c r="G13" t="n">
-        <v>0.98215273545779</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -2704,21 +2410,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>0.173626373626374</v>
+        <v>-0.0901098901098901</v>
       </c>
       <c r="E14" t="n">
-        <v>0.61073549793191</v>
+        <v>-0.313424881933839</v>
       </c>
       <c r="F14" t="n">
-        <v>0.552766941142241</v>
+        <v>0.759338837815954</v>
       </c>
       <c r="G14" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -2727,21 +2433,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>0.279120879120879</v>
+        <v>0.107692307692308</v>
       </c>
       <c r="E15" t="n">
-        <v>1.00692223194835</v>
+        <v>0.375239387193228</v>
       </c>
       <c r="F15" t="n">
-        <v>0.333845077194554</v>
+        <v>0.714030808726249</v>
       </c>
       <c r="G15" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -2750,21 +2456,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0241758241758242</v>
+        <v>-0.0461538461538462</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0837719962821407</v>
+        <v>-0.160052173656655</v>
       </c>
       <c r="F16" t="n">
-        <v>0.934618994603643</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G16" t="n">
-        <v>0.98215273545779</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -2773,21 +2479,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.107692307692308</v>
+        <v>0.151648351648352</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.375239387193228</v>
+        <v>0.531472035224587</v>
       </c>
       <c r="F17" t="n">
-        <v>0.714030808726249</v>
+        <v>0.604790598452137</v>
       </c>
       <c r="G17" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -2796,21 +2502,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0241758241758242</v>
+        <v>0.230769230769231</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0837719962821407</v>
+        <v>0.821583836257749</v>
       </c>
       <c r="F18" t="n">
-        <v>0.934618994603643</v>
+        <v>0.42733586167745</v>
       </c>
       <c r="G18" t="n">
-        <v>0.98215273545779</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -2819,21 +2525,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.362637362637363</v>
       </c>
       <c r="E19" t="n">
-        <v>0.267261241912424</v>
+        <v>1.34796843802067</v>
       </c>
       <c r="F19" t="n">
-        <v>0.793805888355453</v>
+        <v>0.202564543817242</v>
       </c>
       <c r="G19" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -2842,21 +2548,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.103296703296703</v>
+        <v>0.182417582417582</v>
       </c>
       <c r="E20" t="n">
-        <v>0.359754753325688</v>
+        <v>0.642696755708738</v>
       </c>
       <c r="F20" t="n">
-        <v>0.725282211088945</v>
+        <v>0.532508818518694</v>
       </c>
       <c r="G20" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -2865,21 +2571,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.362637362637363</v>
+        <v>-0.0901098901098901</v>
       </c>
       <c r="E21" t="n">
-        <v>1.34796843802067</v>
+        <v>-0.313424881933839</v>
       </c>
       <c r="F21" t="n">
-        <v>0.202564543817242</v>
+        <v>0.759338837815954</v>
       </c>
       <c r="G21" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -2888,21 +2594,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.397802197802198</v>
+        <v>-0.138461538461538</v>
       </c>
       <c r="E22" t="n">
-        <v>1.50198418094989</v>
+        <v>-0.484309802250568</v>
       </c>
       <c r="F22" t="n">
-        <v>0.158950774510835</v>
+        <v>0.636884991265018</v>
       </c>
       <c r="G22" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -2911,21 +2617,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.16043956043956</v>
+        <v>-0.186813186813187</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.563073178275514</v>
+        <v>-0.658736619548309</v>
       </c>
       <c r="F23" t="n">
-        <v>0.583752752641341</v>
+        <v>0.522504012379159</v>
       </c>
       <c r="G23" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -2934,21 +2640,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.235164835164835</v>
+        <v>-0.0461538461538462</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.838140102702703</v>
+        <v>-0.160052173656655</v>
       </c>
       <c r="F24" t="n">
-        <v>0.418333896198592</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G24" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -2957,21 +2663,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.336263736263736</v>
+        <v>-0.182417582417582</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.23687779440215</v>
+        <v>-0.642696755708738</v>
       </c>
       <c r="F25" t="n">
-        <v>0.239792202257253</v>
+        <v>0.532508818518694</v>
       </c>
       <c r="G25" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -2980,21 +2686,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.147252747252747</v>
+        <v>-0.120879120879121</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.515720400699903</v>
+        <v>-0.421830743866054</v>
       </c>
       <c r="F26" t="n">
-        <v>0.615418762484725</v>
+        <v>0.680607020062893</v>
       </c>
       <c r="G26" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -3003,21 +2709,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.186813186813187</v>
+        <v>0.283516483516484</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.658736619548309</v>
+        <v>1.0241536325576</v>
       </c>
       <c r="F27" t="n">
-        <v>0.522504012379159</v>
+        <v>0.325965947441773</v>
       </c>
       <c r="G27" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -3026,21 +2732,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0153846153846154</v>
+        <v>-0.0153846153846154</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0533001790889026</v>
+        <v>-0.0533001790889026</v>
       </c>
       <c r="F28" t="n">
         <v>0.958369789371986</v>
       </c>
       <c r="G28" t="n">
-        <v>0.98215273545779</v>
+        <v>0.958369789371986</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -3049,21 +2755,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.208791208791209</v>
+        <v>-0.0461538461538462</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.739573996953447</v>
+        <v>-0.160052173656655</v>
       </c>
       <c r="F29" t="n">
-        <v>0.473778837309814</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G29" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -3072,21 +2778,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.353846153846154</v>
+        <v>0.485714285714286</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.31054662928584</v>
+        <v>1.92487095804581</v>
       </c>
       <c r="F30" t="n">
-        <v>0.214539870881246</v>
+        <v>0.0782758864586334</v>
       </c>
       <c r="G30" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -3095,21 +2801,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.164835164835165</v>
+        <v>0.243956043956044</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.578924798693409</v>
+        <v>0.871417274558076</v>
       </c>
       <c r="F31" t="n">
-        <v>0.573346405013138</v>
+        <v>0.400624803916119</v>
       </c>
       <c r="G31" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -3118,21 +2824,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00659340659340659</v>
+        <v>-0.243956043956044</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0228407269124562</v>
+        <v>-0.871417274558076</v>
       </c>
       <c r="F32" t="n">
-        <v>0.98215273545779</v>
+        <v>0.400624803916119</v>
       </c>
       <c r="G32" t="n">
-        <v>0.98215273545779</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -3141,21 +2847,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0637362637362637</v>
+        <v>0.112087912087912</v>
       </c>
       <c r="E33" t="n">
-        <v>0.221238721732763</v>
+        <v>0.390746285420994</v>
       </c>
       <c r="F33" t="n">
-        <v>0.828626422928612</v>
+        <v>0.70283316319677</v>
       </c>
       <c r="G33" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -3164,154 +2870,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.323076923076923</v>
+        <v>-0.353846153846154</v>
       </c>
       <c r="E34" t="n">
-        <v>1.18259041285079</v>
+        <v>-1.31054662928584</v>
       </c>
       <c r="F34" t="n">
-        <v>0.25987361950879</v>
+        <v>0.214539870881246</v>
       </c>
       <c r="G34" t="n">
-        <v>0.979285772551996</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.415384615384615</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.58186229790063</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.139665947517526</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.979285772551996</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.248351648351648</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.888140849482722</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.391919538938457</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.979285772551996</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.267261241912424</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.793805888355453</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.979285772551996</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.257142857142857</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.92176480169854</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.37481190387997</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.979285772551996</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.112087912087912</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.390746285420994</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.70283316319677</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.979285772551996</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.230769230769231</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.821583836257749</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.42733586167745</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.979285772551996</v>
+        <v>0.902861991933118</v>
       </c>
     </row>
   </sheetData>
@@ -3350,7 +2918,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -3359,21 +2927,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.389010989010989</v>
+        <v>-0.345054945054945</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.46279326565877</v>
+        <v>-1.27352194297108</v>
       </c>
       <c r="F2" t="n">
-        <v>0.16921738979769</v>
+        <v>0.226948680041701</v>
       </c>
       <c r="G2" t="n">
-        <v>0.324087680010892</v>
+        <v>0.394174023230322</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -3382,21 +2950,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0725274725274725</v>
+        <v>0.327472527472527</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.251905950462024</v>
+        <v>1.20059825800301</v>
       </c>
       <c r="F3" t="n">
-        <v>0.805376313541092</v>
+        <v>0.25307100077194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.937128567984997</v>
+        <v>0.397683001213049</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -3405,21 +2973,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.186813186813187</v>
+        <v>0.274725274725275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.658736619548309</v>
+        <v>0.98975947808112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.522504012379159</v>
+        <v>0.341829743719481</v>
       </c>
       <c r="G4" t="n">
-        <v>0.727773445813829</v>
+        <v>0.490451371423604</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -3428,21 +2996,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.384615384615385</v>
+        <v>0.362637362637363</v>
       </c>
       <c r="E5" t="n">
-        <v>1.44337567297406</v>
+        <v>1.34796843802067</v>
       </c>
       <c r="F5" t="n">
-        <v>0.174508750775096</v>
+        <v>0.202564543817242</v>
       </c>
       <c r="G5" t="n">
-        <v>0.324087680010892</v>
+        <v>0.382246562116407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -3451,21 +3019,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.402197802197802</v>
+        <v>-0.410989010989011</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.52176265267817</v>
+        <v>-1.56169895075115</v>
       </c>
       <c r="F6" t="n">
-        <v>0.153974429541404</v>
+        <v>0.144332668124605</v>
       </c>
       <c r="G6" t="n">
-        <v>0.324087680010892</v>
+        <v>0.382246562116407</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -3474,21 +3042,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0285714285714286</v>
+        <v>-0.389010989010989</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0990147542976674</v>
+        <v>-1.46279326565877</v>
       </c>
       <c r="F7" t="n">
-        <v>0.922761376569875</v>
+        <v>0.16921738979769</v>
       </c>
       <c r="G7" t="n">
-        <v>0.972640369897976</v>
+        <v>0.382246562116407</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -3497,21 +3065,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.397802197802198</v>
+        <v>-0.327472527472527</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.50198418094989</v>
+        <v>-1.20059825800301</v>
       </c>
       <c r="F8" t="n">
-        <v>0.158950774510835</v>
+        <v>0.25307100077194</v>
       </c>
       <c r="G8" t="n">
-        <v>0.324087680010892</v>
+        <v>0.397683001213049</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -3520,21 +3088,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.450549450549451</v>
+        <v>-0.186813186813187</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.74824587411601</v>
+        <v>-0.658736619548309</v>
       </c>
       <c r="F9" t="n">
-        <v>0.105932785272641</v>
+        <v>0.522504012379159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.289687155189012</v>
+        <v>0.664270373695319</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -3543,21 +3111,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.349450549450549</v>
+        <v>0.16043956043956</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2919856983087</v>
+        <v>0.563073178275514</v>
       </c>
       <c r="F10" t="n">
-        <v>0.220689997746447</v>
+        <v>0.583752752641341</v>
       </c>
       <c r="G10" t="n">
-        <v>0.358621246337977</v>
+        <v>0.664270373695319</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -3566,21 +3134,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0505494505494506</v>
+        <v>0.0461538461538462</v>
       </c>
       <c r="E11" t="n">
-        <v>0.175332585602767</v>
+        <v>0.160052173656655</v>
       </c>
       <c r="F11" t="n">
-        <v>0.863742036179215</v>
+        <v>0.875502537632114</v>
       </c>
       <c r="G11" t="n">
-        <v>0.962455411742554</v>
+        <v>0.927189756254403</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -3589,21 +3157,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.52967032967033</v>
+        <v>0.16043956043956</v>
       </c>
       <c r="E12" t="n">
-        <v>2.16319743410023</v>
+        <v>0.563073178275514</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0514165981378708</v>
+        <v>0.583752752641341</v>
       </c>
       <c r="G12" t="n">
-        <v>0.21900031664044</v>
+        <v>0.664270373695319</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -3612,21 +3180,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0373626373626374</v>
+        <v>-0.371428571428571</v>
       </c>
       <c r="E13" t="n">
-        <v>0.12951840569399</v>
+        <v>-1.38580465631147</v>
       </c>
       <c r="F13" t="n">
-        <v>0.899093096973967</v>
+        <v>0.191020812043616</v>
       </c>
       <c r="G13" t="n">
-        <v>0.972640369897976</v>
+        <v>0.382246562116407</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -3635,21 +3203,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0021978021978022</v>
+        <v>0.793406593406593</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00761342853088536</v>
+        <v>4.5153229593002</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9940505286659</v>
+        <v>0.000707534135618204</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9940505286659</v>
+        <v>0.0176645525734471</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -3658,21 +3226,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.534065934065934</v>
+        <v>0.16043956043956</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.18827175544225</v>
+        <v>0.563073178275514</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0491599163719851</v>
+        <v>0.583752752641341</v>
       </c>
       <c r="G15" t="n">
-        <v>0.21900031664044</v>
+        <v>0.664270373695319</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -3681,21 +3249,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.103296703296703</v>
+        <v>0.0857142857142857</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.359754753325688</v>
+        <v>0.298019780339635</v>
       </c>
       <c r="F16" t="n">
-        <v>0.725282211088945</v>
+        <v>0.770785031118676</v>
       </c>
       <c r="G16" t="n">
-        <v>0.912451813950608</v>
+        <v>0.847863534230543</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -3704,21 +3272,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.23956043956044</v>
+        <v>-0.446153846153846</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.854750807147626</v>
+        <v>-1.7269248691087</v>
       </c>
       <c r="F17" t="n">
-        <v>0.409429892851733</v>
+        <v>0.109807127801225</v>
       </c>
       <c r="G17" t="n">
-        <v>0.591398734119169</v>
+        <v>0.362363521744043</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -3727,21 +3295,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0.876923076923077</v>
+        <v>-0.538461538461538</v>
       </c>
       <c r="E18" t="n">
-        <v>6.3203418666616</v>
+        <v>-2.21359436211787</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0000382969810544994</v>
+        <v>0.0469761458595552</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00110756468719485</v>
+        <v>0.172245868151702</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -3750,21 +3318,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.494505494505494</v>
+        <v>-0.30989010989011</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.97085542334902</v>
+        <v>-1.12907237530428</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0722496740341326</v>
+        <v>0.280933280869258</v>
       </c>
       <c r="G19" t="n">
-        <v>0.256157935211925</v>
+        <v>0.421399921303888</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -3773,21 +3341,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0725274725274725</v>
+        <v>-0.0373626373626374</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.251905950462024</v>
+        <v>-0.12951840569399</v>
       </c>
       <c r="F20" t="n">
-        <v>0.805376313541092</v>
+        <v>0.899093096973967</v>
       </c>
       <c r="G20" t="n">
-        <v>0.937128567984997</v>
+        <v>0.927189756254403</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -3796,21 +3364,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.305494505494505</v>
+        <v>0.564835164835165</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.11139556517412</v>
+        <v>2.37110700956328</v>
       </c>
       <c r="F21" t="n">
-        <v>0.288169885875457</v>
+        <v>0.0353301848675528</v>
       </c>
       <c r="G21" t="n">
-        <v>0.449545021965713</v>
+        <v>0.145737012578655</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -3819,21 +3387,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.476923076923077</v>
+        <v>0.00659340659340659</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.87965109403158</v>
+        <v>0.0228407269124562</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0846484341946867</v>
+        <v>0.98215273545779</v>
       </c>
       <c r="G22" t="n">
-        <v>0.275107411132732</v>
+        <v>0.98215273545779</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -3842,21 +3410,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>0.147252747252747</v>
+        <v>-0.217582417582418</v>
       </c>
       <c r="E23" t="n">
-        <v>0.515720400699903</v>
+        <v>-0.772228696551556</v>
       </c>
       <c r="F23" t="n">
-        <v>0.615418762484725</v>
+        <v>0.454919373170033</v>
       </c>
       <c r="G23" t="n">
-        <v>0.827632128858768</v>
+        <v>0.625514138108795</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -3865,21 +3433,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.432967032967033</v>
+        <v>-0.753846153846154</v>
       </c>
       <c r="E24" t="n">
-        <v>1.66388458531666</v>
+        <v>-3.97442481770368</v>
       </c>
       <c r="F24" t="n">
-        <v>0.12201000596848</v>
+        <v>0.00184472528925722</v>
       </c>
       <c r="G24" t="n">
-        <v>0.289687155189012</v>
+        <v>0.0176645525734471</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -3888,21 +3456,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>0.248351648351648</v>
+        <v>0.582417582417582</v>
       </c>
       <c r="E25" t="n">
-        <v>0.888140849482722</v>
+        <v>2.48195240069149</v>
       </c>
       <c r="F25" t="n">
-        <v>0.391919538938457</v>
+        <v>0.0288546553576718</v>
       </c>
       <c r="G25" t="n">
-        <v>0.587879308407686</v>
+        <v>0.13602908954331</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -3911,21 +3479,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.010989010989011</v>
+        <v>-0.753846153846154</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0380693493813441</v>
+        <v>-3.97442481770368</v>
       </c>
       <c r="F26" t="n">
-        <v>0.970258390096969</v>
+        <v>0.00184472528925722</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9940505286659</v>
+        <v>0.0176645525734471</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -3934,21 +3502,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.520879120879121</v>
+        <v>0.745054945054945</v>
       </c>
       <c r="E27" t="n">
-        <v>2.11376973320625</v>
+        <v>3.86946636014232</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0561539273437027</v>
+        <v>0.00223003731674207</v>
       </c>
       <c r="G27" t="n">
-        <v>0.21900031664044</v>
+        <v>0.0176645525734471</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -3957,21 +3525,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.428571428571429</v>
+        <v>-0.736263736263736</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.6431676725155</v>
+        <v>-3.76904446810218</v>
       </c>
       <c r="F28" t="n">
-        <v>0.126273888159313</v>
+        <v>0.00267644735961319</v>
       </c>
       <c r="G28" t="n">
-        <v>0.289687155189012</v>
+        <v>0.0176645525734471</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -3980,21 +3548,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.868131868131868</v>
+        <v>-0.402197802197802</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.05902341189422</v>
+        <v>-1.52176265267817</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0000567981890869155</v>
+        <v>0.153974429541404</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00110756468719485</v>
+        <v>0.382246562116407</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -4003,21 +3571,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.613186813186813</v>
+        <v>0.358241758241758</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.68899789613342</v>
+        <v>1.32920682989838</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0197063319260388</v>
+        <v>0.208498124790767</v>
       </c>
       <c r="G30" t="n">
-        <v>0.128091157519253</v>
+        <v>0.382246562116407</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -4026,21 +3594,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>0.595604395604396</v>
+        <v>-0.173626373626374</v>
       </c>
       <c r="E31" t="n">
-        <v>2.56851846406669</v>
+        <v>-0.61073549793191</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0246126107952868</v>
+        <v>0.552766941142241</v>
       </c>
       <c r="G31" t="n">
-        <v>0.137127403002312</v>
+        <v>0.664270373695319</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -4049,21 +3617,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.74945054945055</v>
+        <v>0.384615384615385</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.92135393228648</v>
+        <v>1.44337567297406</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00203014554910065</v>
+        <v>0.174508750775096</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0197939191037313</v>
+        <v>0.382246562116407</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -4072,21 +3640,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.362637362637363</v>
+        <v>0.371428571428571</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.34796843802067</v>
+        <v>1.38580465631147</v>
       </c>
       <c r="F33" t="n">
-        <v>0.202564543817242</v>
+        <v>0.191020812043616</v>
       </c>
       <c r="G33" t="n">
-        <v>0.34347900908141</v>
+        <v>0.382246562116407</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -4095,154 +3663,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0681318681318681</v>
+        <v>-0.661538461538462</v>
       </c>
       <c r="E34" t="n">
-        <v>0.236565415689409</v>
+        <v>-3.05587693443042</v>
       </c>
       <c r="F34" t="n">
-        <v>0.816983879781792</v>
+        <v>0.00997517924042373</v>
       </c>
       <c r="G34" t="n">
-        <v>0.937128567984997</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.428571428571429</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.6431676725155</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.126273888159313</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.289687155189012</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.767032967032967</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4.14128474862473</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.00136768238824561</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.0177798710471929</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.12967032967033</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.453015938607022</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.658619276321178</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.856205059217531</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.70989010989011</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3.4915348503379</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.00445074141876422</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.034715783066361</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.371428571428571</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.38580465631147</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.191020812043616</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.338627803168229</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.463736263736264</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.81318054513692</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.0948763315088996</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.284628994526699</v>
+        <v>0.0548634858223305</v>
       </c>
     </row>
   </sheetData>
@@ -4281,7 +3711,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -4290,21 +3720,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.249450554817483</v>
+        <v>0.368657014641767</v>
       </c>
       <c r="E2" t="n">
-        <v>0.892330846213975</v>
+        <v>1.37383042898264</v>
       </c>
       <c r="F2" t="n">
-        <v>0.389758912148495</v>
+        <v>0.194613697655993</v>
       </c>
       <c r="G2" t="n">
-        <v>0.982073776394341</v>
+        <v>0.80278150283097</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -4313,21 +3743,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.152319365331029</v>
+        <v>-0.0110376351689152</v>
       </c>
       <c r="E3" t="n">
-        <v>0.53387942414767</v>
+        <v>-0.0382378191319795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.603174465292242</v>
+        <v>0.970126842730692</v>
       </c>
       <c r="G3" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -4336,21 +3766,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.147904311263463</v>
+        <v>-0.222960230412086</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.518053281482909</v>
+        <v>-0.79230105983522</v>
       </c>
       <c r="F4" t="n">
-        <v>0.613838845513006</v>
+        <v>0.443566775254162</v>
       </c>
       <c r="G4" t="n">
-        <v>0.982073776394341</v>
+        <v>0.934058013882014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -4359,21 +3789,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0154526892364812</v>
+        <v>-0.483448420398485</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.053536077946302</v>
+        <v>-1.91314415999886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.958185730270463</v>
+        <v>0.0798848632023047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.982073776394341</v>
+        <v>0.615999947121075</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -4382,21 +3812,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.364241960574201</v>
+        <v>0.373072068709333</v>
       </c>
       <c r="E6" t="n">
-        <v>1.35484298188477</v>
+        <v>1.39292547878962</v>
       </c>
       <c r="F6" t="n">
-        <v>0.200425414148861</v>
+        <v>0.188910427363958</v>
       </c>
       <c r="G6" t="n">
-        <v>0.982073776394341</v>
+        <v>0.80278150283097</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -4405,21 +3835,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0507731217770098</v>
+        <v>0.249450554817483</v>
       </c>
       <c r="E7" t="n">
-        <v>0.176110398006348</v>
+        <v>0.892330846213975</v>
       </c>
       <c r="F7" t="n">
-        <v>0.863144281491935</v>
+        <v>0.389758912148495</v>
       </c>
       <c r="G7" t="n">
-        <v>0.982073776394341</v>
+        <v>0.934058013882014</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -4428,21 +3858,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.187639797871558</v>
+        <v>0.32009141989854</v>
       </c>
       <c r="E8" t="n">
-        <v>0.661757525478576</v>
+        <v>1.17040829459932</v>
       </c>
       <c r="F8" t="n">
-        <v>0.520631994545967</v>
+        <v>0.264555978110811</v>
       </c>
       <c r="G8" t="n">
-        <v>0.982073776394341</v>
+        <v>0.873034727765675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -4451,21 +3881,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.333336582101238</v>
+        <v>0.064018283979708</v>
       </c>
       <c r="E9" t="n">
-        <v>1.22475830024356</v>
+        <v>0.222221678529365</v>
       </c>
       <c r="F9" t="n">
-        <v>0.244165215719948</v>
+        <v>0.827878434049954</v>
       </c>
       <c r="G9" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -4474,21 +3904,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.479033366330918</v>
+        <v>-0.44371293379039</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.89043803829291</v>
+        <v>-1.71515275899119</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0830866536778713</v>
+        <v>0.11199999038565</v>
       </c>
       <c r="G10" t="n">
-        <v>0.810094873359245</v>
+        <v>0.615999947121075</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -4497,21 +3927,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.161149473466161</v>
+        <v>-0.0419430136418776</v>
       </c>
       <c r="E11" t="n">
-        <v>0.565630941325089</v>
+        <v>-0.145422832723353</v>
       </c>
       <c r="F11" t="n">
-        <v>0.58206691151376</v>
+        <v>0.886791154908312</v>
       </c>
       <c r="G11" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -4520,21 +3950,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0066225811013491</v>
+        <v>-0.21854517634452</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0229417969924051</v>
+        <v>-0.775816644501819</v>
       </c>
       <c r="F12" t="n">
-        <v>0.982073776394341</v>
+        <v>0.45287661279128</v>
       </c>
       <c r="G12" t="n">
-        <v>0.982073776394341</v>
+        <v>0.934058013882014</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
@@ -4543,21 +3973,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0154526892364812</v>
+        <v>0.483448420398485</v>
       </c>
       <c r="E13" t="n">
-        <v>0.053536077946302</v>
+        <v>1.91314415999886</v>
       </c>
       <c r="F13" t="n">
-        <v>0.958185730270463</v>
+        <v>0.0798848632023047</v>
       </c>
       <c r="G13" t="n">
-        <v>0.982073776394341</v>
+        <v>0.615999947121075</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -4566,21 +3996,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.249450554817483</v>
+        <v>-0.187639797871558</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.892330846213975</v>
+        <v>-0.661757525478576</v>
       </c>
       <c r="F14" t="n">
-        <v>0.389758912148495</v>
+        <v>0.520631994545967</v>
       </c>
       <c r="G14" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
@@ -4589,21 +4019,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0110376351689152</v>
+        <v>0.346581744303936</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0382378191319795</v>
+        <v>1.27992438410647</v>
       </c>
       <c r="F15" t="n">
-        <v>0.970126842730692</v>
+        <v>0.224762432799956</v>
       </c>
       <c r="G15" t="n">
-        <v>0.982073776394341</v>
+        <v>0.824128920266504</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
@@ -4612,21 +4042,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>0.598239826155202</v>
+        <v>0.227375284479653</v>
       </c>
       <c r="E16" t="n">
-        <v>2.58619655411111</v>
+        <v>0.808836783143875</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0238242680270559</v>
+        <v>0.434352877581203</v>
       </c>
       <c r="G16" t="n">
-        <v>0.46457322652759</v>
+        <v>0.934058013882014</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
@@ -4635,21 +4065,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0860935543175383</v>
+        <v>0.483448420398485</v>
       </c>
       <c r="E17" t="n">
-        <v>0.299348283684926</v>
+        <v>1.91314415999886</v>
       </c>
       <c r="F17" t="n">
-        <v>0.769795666502862</v>
+        <v>0.0798848632023047</v>
       </c>
       <c r="G17" t="n">
-        <v>0.982073776394341</v>
+        <v>0.615999947121075</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B18" t="n">
         <v>14</v>
@@ -4658,21 +4088,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.178809689736426</v>
+        <v>-0.0375279595743116</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.629561144169653</v>
+        <v>-0.130092305253455</v>
       </c>
       <c r="F18" t="n">
-        <v>0.540783051363236</v>
+        <v>0.898648693337954</v>
       </c>
       <c r="G18" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B19" t="n">
         <v>14</v>
@@ -4681,21 +4111,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.359826906506635</v>
+        <v>0.58940971802007</v>
       </c>
       <c r="E19" t="n">
-        <v>1.33596085998907</v>
+        <v>2.52746790861781</v>
       </c>
       <c r="F19" t="n">
-        <v>0.20634589204536</v>
+        <v>0.0265425999720271</v>
       </c>
       <c r="G19" t="n">
-        <v>0.982073776394341</v>
+        <v>0.615999947121075</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -4704,21 +4134,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>0.116998932790501</v>
+        <v>0.293601095493144</v>
       </c>
       <c r="E20" t="n">
-        <v>0.408098999478513</v>
+        <v>1.06395460557189</v>
       </c>
       <c r="F20" t="n">
-        <v>0.69038852169286</v>
+        <v>0.308290791512181</v>
       </c>
       <c r="G20" t="n">
-        <v>0.982073776394341</v>
+        <v>0.924872374536542</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B21" t="n">
         <v>14</v>
@@ -4727,21 +4157,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>0.532014015141711</v>
+        <v>-0.0596032299121419</v>
       </c>
       <c r="E21" t="n">
-        <v>2.17653624463212</v>
+        <v>-0.206839374986338</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0502042077631658</v>
+        <v>0.839603457315711</v>
       </c>
       <c r="G21" t="n">
-        <v>0.652654700921156</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B22" t="n">
         <v>14</v>
@@ -4750,21 +4180,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.602654880222768</v>
+        <v>-0.44371293379039</v>
       </c>
       <c r="E22" t="n">
-        <v>2.61610610298231</v>
+        <v>-1.71515275899119</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0225462832462468</v>
+        <v>0.11199999038565</v>
       </c>
       <c r="G22" t="n">
-        <v>0.46457322652759</v>
+        <v>0.615999947121075</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -4773,21 +4203,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>0.156734419398595</v>
+        <v>0.116998932790501</v>
       </c>
       <c r="E23" t="n">
-        <v>0.549738288649676</v>
+        <v>0.408098999478513</v>
       </c>
       <c r="F23" t="n">
-        <v>0.592583253617127</v>
+        <v>0.69038852169286</v>
       </c>
       <c r="G23" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B24" t="n">
         <v>14</v>
@@ -4796,21 +4226,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.267110771087747</v>
+        <v>0.0286978514391794</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.960186428446284</v>
+        <v>0.099453235142041</v>
       </c>
       <c r="F24" t="n">
-        <v>0.355909664957315</v>
+        <v>0.922420546666938</v>
       </c>
       <c r="G24" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B25" t="n">
         <v>14</v>
@@ -4819,21 +4249,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.236205392614785</v>
+        <v>0.108168824655369</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.842067334785579</v>
+        <v>0.376919359787956</v>
       </c>
       <c r="F25" t="n">
-        <v>0.416217193383683</v>
+        <v>0.712814265313813</v>
       </c>
       <c r="G25" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -4842,21 +4272,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.434882825655258</v>
+        <v>0.0242827973716134</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.67295942575489</v>
+        <v>0.0841428888590603</v>
       </c>
       <c r="F26" t="n">
-        <v>0.120182559331165</v>
+        <v>0.934330263826498</v>
       </c>
       <c r="G26" t="n">
-        <v>0.937423962783089</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B27" t="n">
         <v>14</v>
@@ -4865,21 +4295,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.121413986858067</v>
+        <v>-0.0772634461824062</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.423725124935532</v>
+        <v>-0.268450905777255</v>
       </c>
       <c r="F27" t="n">
-        <v>0.679262298312358</v>
+        <v>0.79291155545467</v>
       </c>
       <c r="G27" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B28" t="n">
         <v>14</v>
@@ -4888,21 +4318,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0331129055067455</v>
+        <v>0.0949236624526705</v>
       </c>
       <c r="E28" t="n">
-        <v>0.114769406995615</v>
+        <v>0.330316739642975</v>
       </c>
       <c r="F28" t="n">
-        <v>0.910525922192681</v>
+        <v>0.74685613940133</v>
       </c>
       <c r="G28" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B29" t="n">
         <v>14</v>
@@ -4911,21 +4341,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0242827973716134</v>
+        <v>0.0331129055067455</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0841428888590603</v>
+        <v>0.114769406995615</v>
       </c>
       <c r="F29" t="n">
-        <v>0.934330263826498</v>
+        <v>0.910525922192681</v>
       </c>
       <c r="G29" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B30" t="n">
         <v>14</v>
@@ -4934,21 +4364,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0375279595743116</v>
+        <v>0.0110376351689152</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.130092305253455</v>
+        <v>0.0382378191319795</v>
       </c>
       <c r="F30" t="n">
-        <v>0.898648693337954</v>
+        <v>0.970126842730692</v>
       </c>
       <c r="G30" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -4957,21 +4387,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0816785002499723</v>
+        <v>0.17439463566886</v>
       </c>
       <c r="E31" t="n">
-        <v>0.283891181939403</v>
+        <v>0.61352245499117</v>
       </c>
       <c r="F31" t="n">
-        <v>0.781332631337183</v>
+        <v>0.550983597252068</v>
       </c>
       <c r="G31" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B32" t="n">
         <v>14</v>
@@ -4980,21 +4410,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0816785002499723</v>
+        <v>0.240620446682351</v>
       </c>
       <c r="E32" t="n">
-        <v>0.283891181939403</v>
+        <v>0.858764799958283</v>
       </c>
       <c r="F32" t="n">
-        <v>0.781332631337183</v>
+        <v>0.407297445698997</v>
       </c>
       <c r="G32" t="n">
-        <v>0.982073776394341</v>
+        <v>0.934058013882014</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B33" t="n">
         <v>14</v>
@@ -5003,21 +4433,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.116998932790501</v>
+        <v>-0.068433338047274</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.408098999478513</v>
+        <v>-0.237617084674322</v>
       </c>
       <c r="F33" t="n">
-        <v>0.69038852169286</v>
+        <v>0.816186639863922</v>
       </c>
       <c r="G33" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B34" t="n">
         <v>14</v>
@@ -5026,154 +4456,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.165564527533728</v>
+        <v>0.0110376351689152</v>
       </c>
       <c r="E34" t="n">
-        <v>0.581558459234465</v>
+        <v>0.0382378191319795</v>
       </c>
       <c r="F34" t="n">
-        <v>0.571627105910981</v>
+        <v>0.970126842730692</v>
       </c>
       <c r="G34" t="n">
-        <v>0.982073776394341</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.0463580677094437</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.160761894454504</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.874955592511206</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.982073776394341</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-0.0993387165202365</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.345829995327011</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.735457787349676</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.982073776394341</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" t="n">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0728483921148401</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.25302651763146</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.804530283063219</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.982073776394341</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.116998932790501</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.408098999478513</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.69038852169286</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.982073776394341</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" t="n">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.068433338047274</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.237617084674322</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.816186639863922</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.982073776394341</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" t="n">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.275940879222879</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.994499059084995</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.339611058042248</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.982073776394341</v>
+        <v>0.970126842730692</v>
       </c>
     </row>
   </sheetData>
@@ -5212,7 +4504,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B2" t="n">
         <v>13</v>
@@ -5221,21 +4513,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.187328534514529</v>
+        <v>0.104683592816943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.632495325378921</v>
+        <v>0.349114380687211</v>
       </c>
       <c r="F2" t="n">
-        <v>0.539987828132436</v>
+        <v>0.733594691642229</v>
       </c>
       <c r="G2" t="n">
-        <v>0.992873609475608</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
         <v>13</v>
@@ -5244,21 +4536,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.151515726445575</v>
+        <v>0.267218644822196</v>
       </c>
       <c r="E3" t="n">
-        <v>0.508390257746437</v>
+        <v>0.919708324392325</v>
       </c>
       <c r="F3" t="n">
-        <v>0.621220334883396</v>
+        <v>0.377452818615708</v>
       </c>
       <c r="G3" t="n">
-        <v>0.992873609475608</v>
+        <v>0.93787359623002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B4" t="n">
         <v>13</v>
@@ -5267,21 +4559,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.132231906716138</v>
+        <v>0.322315272620587</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.44244884873664</v>
+        <v>1.12926500801572</v>
       </c>
       <c r="F4" t="n">
-        <v>0.666738148259011</v>
+        <v>0.28281102936488</v>
       </c>
       <c r="G4" t="n">
-        <v>0.992873609475608</v>
+        <v>0.801869422011304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
         <v>13</v>
@@ -5290,21 +4582,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.283747633161713</v>
+        <v>0.239670330923</v>
       </c>
       <c r="E5" t="n">
-        <v>0.981421860119893</v>
+        <v>0.818759864872612</v>
       </c>
       <c r="F5" t="n">
-        <v>0.347477774764846</v>
+        <v>0.430304450443239</v>
       </c>
       <c r="G5" t="n">
-        <v>0.992873609475608</v>
+        <v>0.93787359623002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
@@ -5313,21 +4605,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.490359987405679</v>
+        <v>-0.426998865437529</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.86609615387883</v>
+        <v>-1.56615055530539</v>
       </c>
       <c r="F6" t="n">
-        <v>0.088896862355391</v>
+        <v>0.145609709852288</v>
       </c>
       <c r="G6" t="n">
-        <v>0.810080092784433</v>
+        <v>0.707961134595952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -5336,21 +4628,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.388431225978656</v>
+        <v>0.187328534514529</v>
       </c>
       <c r="E7" t="n">
-        <v>1.39805945368633</v>
+        <v>0.632495325378921</v>
       </c>
       <c r="F7" t="n">
-        <v>0.189647138965514</v>
+        <v>0.539987828132436</v>
       </c>
       <c r="G7" t="n">
-        <v>0.810080092784433</v>
+        <v>0.93787359623002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>13</v>
@@ -5359,21 +4651,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.380166731808897</v>
+        <v>-0.0137741569495977</v>
       </c>
       <c r="E8" t="n">
-        <v>1.36322403126279</v>
+        <v>-0.0456880447478406</v>
       </c>
       <c r="F8" t="n">
-        <v>0.200063057417365</v>
+        <v>0.964377780387274</v>
       </c>
       <c r="G8" t="n">
-        <v>0.810080092784433</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B9" t="n">
         <v>13</v>
@@ -5382,21 +4674,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.00275483138991954</v>
+        <v>0.407715045708092</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.00913677675106004</v>
+        <v>1.48091575833618</v>
       </c>
       <c r="F9" t="n">
-        <v>0.992873609475608</v>
+        <v>0.166694809700976</v>
       </c>
       <c r="G9" t="n">
-        <v>0.992873609475608</v>
+        <v>0.707961134595952</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B10" t="n">
         <v>13</v>
@@ -5405,21 +4697,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.192838197294368</v>
+        <v>0.672178859140368</v>
       </c>
       <c r="E10" t="n">
-        <v>0.651805972865789</v>
+        <v>3.01107344580734</v>
       </c>
       <c r="F10" t="n">
-        <v>0.52791023374094</v>
+        <v>0.0118431273166881</v>
       </c>
       <c r="G10" t="n">
-        <v>0.992873609475608</v>
+        <v>0.195411600725353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -5428,21 +4720,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.146006063665736</v>
+        <v>-0.680443353310127</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.489492885305727</v>
+        <v>-3.0796577327477</v>
       </c>
       <c r="F11" t="n">
-        <v>0.634107747881102</v>
+        <v>0.0104777044732212</v>
       </c>
       <c r="G11" t="n">
-        <v>0.992873609475608</v>
+        <v>0.195411600725353</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
@@ -5451,21 +4743,21 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.347108755129862</v>
+        <v>-0.168044714785092</v>
       </c>
       <c r="E12" t="n">
-        <v>1.22755273662222</v>
+        <v>-0.565381343686788</v>
       </c>
       <c r="F12" t="n">
-        <v>0.24523667536081</v>
+        <v>0.583162224560326</v>
       </c>
       <c r="G12" t="n">
-        <v>0.810080092784433</v>
+        <v>0.962217670524539</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B13" t="n">
         <v>13</v>
@@ -5474,21 +4766,21 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.707991667209323</v>
+        <v>-0.223141342583483</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.32494137811659</v>
+        <v>-0.759218979815034</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00677170621027268</v>
+        <v>0.463680868313643</v>
       </c>
       <c r="G13" t="n">
-        <v>0.264096542200634</v>
+        <v>0.93787359623002</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B14" t="n">
         <v>13</v>
@@ -5497,21 +4789,21 @@
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>0.42424403404761</v>
+        <v>0.319560441230667</v>
       </c>
       <c r="E14" t="n">
-        <v>1.55381982571673</v>
+        <v>1.11851016120951</v>
       </c>
       <c r="F14" t="n">
-        <v>0.148508964378181</v>
+        <v>0.287180591013506</v>
       </c>
       <c r="G14" t="n">
-        <v>0.810080092784433</v>
+        <v>0.801869422011304</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B15" t="n">
         <v>13</v>
@@ -5520,21 +4812,21 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0550966277983909</v>
+        <v>-0.402205382928253</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.183012833143425</v>
+        <v>-1.4570095764288</v>
       </c>
       <c r="F15" t="n">
-        <v>0.858117503842751</v>
+        <v>0.173060593753027</v>
       </c>
       <c r="G15" t="n">
-        <v>0.992873609475608</v>
+        <v>0.707961134595952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B16" t="n">
         <v>13</v>
@@ -5543,21 +4835,21 @@
         <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.380166731808897</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.36322403126279</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.200063057417365</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.810080092784433</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B17" t="n">
         <v>13</v>
@@ -5566,21 +4858,21 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.371902237639138</v>
+        <v>-0.198347860074207</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.32877034966001</v>
+        <v>-0.671180656324928</v>
       </c>
       <c r="F17" t="n">
-        <v>0.210829007788001</v>
+        <v>0.515951994239241</v>
       </c>
       <c r="G17" t="n">
-        <v>0.810080092784433</v>
+        <v>0.93787359623002</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B18" t="n">
         <v>13</v>
@@ -5589,21 +4881,21 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0.344353923739943</v>
+        <v>-0.0110193255596782</v>
       </c>
       <c r="E18" t="n">
-        <v>1.21649362034641</v>
+        <v>-0.0365491873939215</v>
       </c>
       <c r="F18" t="n">
-        <v>0.249255413164441</v>
+        <v>0.971499304756066</v>
       </c>
       <c r="G18" t="n">
-        <v>0.810080092784433</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B19" t="n">
         <v>13</v>
@@ -5612,21 +4904,21 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.247934825092759</v>
+        <v>-0.00275483138991954</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.848809405727619</v>
+        <v>-0.00913677675106004</v>
       </c>
       <c r="F19" t="n">
-        <v>0.414077790889074</v>
+        <v>0.992873609475608</v>
       </c>
       <c r="G19" t="n">
-        <v>0.992873609475608</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B20" t="n">
         <v>13</v>
@@ -5635,21 +4927,21 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.54545661520407</v>
+        <v>-0.112948086986701</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.15844246164869</v>
+        <v>-0.377019011251611</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0538500889676198</v>
+        <v>0.713331564734471</v>
       </c>
       <c r="G20" t="n">
-        <v>0.810080092784433</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B21" t="n">
         <v>13</v>
@@ -5658,21 +4950,21 @@
         <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.126722243936299</v>
+        <v>-0.00826449416975863</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.423705951221972</v>
+        <v>-0.027411162375895</v>
       </c>
       <c r="F21" t="n">
-        <v>0.679946830063288</v>
+        <v>0.978622775276868</v>
       </c>
       <c r="G21" t="n">
-        <v>0.992873609475608</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B22" t="n">
         <v>13</v>
@@ -5681,21 +4973,21 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.00275483138991954</v>
+        <v>0.146006063665736</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.00913677675106004</v>
+        <v>0.489492885305727</v>
       </c>
       <c r="F22" t="n">
-        <v>0.992873609475608</v>
+        <v>0.634107747881102</v>
       </c>
       <c r="G22" t="n">
-        <v>0.992873609475608</v>
+        <v>0.996455032384589</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B23" t="n">
         <v>13</v>
@@ -5704,21 +4996,21 @@
         <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0991739300371035</v>
+        <v>-0.457302010726644</v>
       </c>
       <c r="E23" t="n">
-        <v>0.330552300103641</v>
+        <v>-1.70547581527748</v>
       </c>
       <c r="F23" t="n">
-        <v>0.747193138520109</v>
+        <v>0.116147049352631</v>
       </c>
       <c r="G23" t="n">
-        <v>0.992873609475608</v>
+        <v>0.707961134595952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B24" t="n">
         <v>13</v>
@@ -5727,21 +5019,21 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00550966277983909</v>
+        <v>-0.0413224708487931</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0182737615268783</v>
+        <v>-0.137168291876545</v>
       </c>
       <c r="F24" t="n">
-        <v>0.985747705683119</v>
+        <v>0.893376232470295</v>
       </c>
       <c r="G24" t="n">
-        <v>0.992873609475608</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B25" t="n">
         <v>13</v>
@@ -5750,21 +5042,21 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>0.137741569495977</v>
+        <v>0.0853997730875058</v>
       </c>
       <c r="E25" t="n">
-        <v>0.461233488293909</v>
+        <v>0.284277536784556</v>
       </c>
       <c r="F25" t="n">
-        <v>0.653617322630365</v>
+        <v>0.781477753040576</v>
       </c>
       <c r="G25" t="n">
-        <v>0.992873609475608</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B26" t="n">
         <v>13</v>
@@ -5773,21 +5065,21 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>0.146006063665736</v>
+        <v>-0.385676394588736</v>
       </c>
       <c r="E26" t="n">
-        <v>0.489492885305727</v>
+        <v>-1.38640427897596</v>
       </c>
       <c r="F26" t="n">
-        <v>0.634107747881102</v>
+        <v>0.19308030943526</v>
       </c>
       <c r="G26" t="n">
-        <v>0.992873609475608</v>
+        <v>0.707961134595952</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B27" t="n">
         <v>13</v>
@@ -5796,21 +5088,21 @@
         <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0330579766790345</v>
+        <v>0.0853997730875058</v>
       </c>
       <c r="E27" t="n">
-        <v>0.109700863545881</v>
+        <v>0.284277536784556</v>
       </c>
       <c r="F27" t="n">
-        <v>0.914622363832917</v>
+        <v>0.781477753040576</v>
       </c>
       <c r="G27" t="n">
-        <v>0.992873609475608</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B28" t="n">
         <v>13</v>
@@ -5819,21 +5111,21 @@
         <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>0.201102691464127</v>
+        <v>-0.206612354243966</v>
       </c>
       <c r="E28" t="n">
-        <v>0.680892697615746</v>
+        <v>-0.700367570122216</v>
       </c>
       <c r="F28" t="n">
-        <v>0.51001840143134</v>
+        <v>0.498243766383061</v>
       </c>
       <c r="G28" t="n">
-        <v>0.992873609475608</v>
+        <v>0.93787359623002</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B29" t="n">
         <v>13</v>
@@ -5842,21 +5134,21 @@
         <v>35</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.184573703124609</v>
+        <v>0.228651005363322</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.622863336791807</v>
+        <v>0.778986136706131</v>
       </c>
       <c r="F29" t="n">
-        <v>0.546070597223801</v>
+        <v>0.452420842793172</v>
       </c>
       <c r="G29" t="n">
-        <v>0.992873609475608</v>
+        <v>0.93787359623002</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B30" t="n">
         <v>13</v>
@@ -5865,21 +5157,21 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.440773022387127</v>
+        <v>0.396695720148414</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.62861903766937</v>
+        <v>1.43329225233257</v>
       </c>
       <c r="F30" t="n">
-        <v>0.131670063728517</v>
+        <v>0.179579653748722</v>
       </c>
       <c r="G30" t="n">
-        <v>0.810080092784433</v>
+        <v>0.707961134595952</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B31" t="n">
         <v>13</v>
@@ -5888,21 +5180,21 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>0.112948086986701</v>
+        <v>0.316805609840748</v>
       </c>
       <c r="E31" t="n">
-        <v>0.377019011251611</v>
+        <v>1.10778690220166</v>
       </c>
       <c r="F31" t="n">
-        <v>0.713331564734471</v>
+        <v>0.291588880731383</v>
       </c>
       <c r="G31" t="n">
-        <v>0.992873609475608</v>
+        <v>0.801869422011304</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B32" t="n">
         <v>13</v>
@@ -5911,21 +5203,21 @@
         <v>38</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.165289883395173</v>
+        <v>0.06060629057823</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.555850229432985</v>
+        <v>0.201378509992724</v>
       </c>
       <c r="F32" t="n">
-        <v>0.589440177662372</v>
+        <v>0.844078120732535</v>
       </c>
       <c r="G32" t="n">
-        <v>0.992873609475608</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B33" t="n">
         <v>13</v>
@@ -5934,21 +5226,21 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.112948086986701</v>
+        <v>0.00826449416975863</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.377019011251611</v>
+        <v>0.027411162375895</v>
       </c>
       <c r="F33" t="n">
-        <v>0.713331564734471</v>
+        <v>0.978622775276868</v>
       </c>
       <c r="G33" t="n">
-        <v>0.992873609475608</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B34" t="n">
         <v>13</v>
@@ -5957,154 +5249,16 @@
         <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>0.231405836753242</v>
+        <v>-0.471076167676242</v>
       </c>
       <c r="E34" t="n">
-        <v>0.788899183589376</v>
+        <v>-1.77122334665281</v>
       </c>
       <c r="F34" t="n">
-        <v>0.446840921762623</v>
+        <v>0.104190107063882</v>
       </c>
       <c r="G34" t="n">
-        <v>0.992873609475608</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" t="n">
-        <v>13</v>
-      </c>
-      <c r="C35" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.429753696827449</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.57853461767748</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.142747751241424</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.810080092784433</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" t="n">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.0743804475278277</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.247377286636928</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.80917280774685</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.992873609475608</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" t="n">
-        <v>13</v>
-      </c>
-      <c r="C37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0440773022387127</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.146330088079287</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.886308065432777</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.992873609475608</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" t="n">
-        <v>13</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0165289883395173</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.0548279426993271</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.957258688126924</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.992873609475608</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" t="n">
-        <v>13</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.00826449416975863</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.027411162375895</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.978622775276868</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.992873609475608</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" t="n">
-        <v>13</v>
-      </c>
-      <c r="C40" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.0413224708487931</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.137168291876545</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.893376232470295</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.992873609475608</v>
+        <v>0.707961134595952</v>
       </c>
     </row>
   </sheetData>
@@ -6120,123 +5274,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.164835164835165</v>
+        <v>0.169230769230769</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.165289883395173</v>
+        <v>0.206612354243966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.147904311263463</v>
+        <v>0.187639797871558</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -6245,59 +5399,59 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.169230769230769</v>
+        <v>0.147252747252747</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.173626373626374</v>
+        <v>0.138461538461538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.389010989010989</v>
+        <v>0.362637362637363</v>
       </c>
     </row>
   </sheetData>
